--- a/result/verified/j30_Bimerge_BDD_paraFROST.xlsx
+++ b/result/verified/j30_Bimerge_BDD_paraFROST.xlsx
@@ -2478,9 +2478,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2805,30 +2811,40 @@
   <sheetPr filterMode="1"/>
   <dimension ref="A1:I641"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="3" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -5448,6 +5464,7 @@
       <c r="D102">
         <v>1024176</v>
       </c>
+      <c r="E102"/>
       <c r="F102" t="s">
         <v>114</v>
       </c>
@@ -5471,6 +5488,7 @@
       <c r="D103">
         <v>1207672</v>
       </c>
+      <c r="E103"/>
       <c r="F103" t="s">
         <v>114</v>
       </c>
@@ -5494,6 +5512,7 @@
       <c r="D104">
         <v>1206625</v>
       </c>
+      <c r="E104"/>
       <c r="F104" t="s">
         <v>114</v>
       </c>
@@ -5517,6 +5536,7 @@
       <c r="D105">
         <v>1129965</v>
       </c>
+      <c r="E105"/>
       <c r="F105" t="s">
         <v>114</v>
       </c>
@@ -5540,6 +5560,7 @@
       <c r="D106">
         <v>1083185</v>
       </c>
+      <c r="E106"/>
       <c r="F106" t="s">
         <v>114</v>
       </c>
@@ -5563,6 +5584,7 @@
       <c r="D107">
         <v>1132218</v>
       </c>
+      <c r="E107"/>
       <c r="F107" t="s">
         <v>114</v>
       </c>
@@ -5586,6 +5608,7 @@
       <c r="D108">
         <v>1201885</v>
       </c>
+      <c r="E108"/>
       <c r="F108" t="s">
         <v>114</v>
       </c>
@@ -5609,6 +5632,7 @@
       <c r="D109">
         <v>1179823</v>
       </c>
+      <c r="E109"/>
       <c r="F109" t="s">
         <v>114</v>
       </c>
@@ -5632,6 +5656,7 @@
       <c r="D110">
         <v>969556</v>
       </c>
+      <c r="E110"/>
       <c r="F110" t="s">
         <v>114</v>
       </c>
@@ -5655,6 +5680,7 @@
       <c r="D111">
         <v>1238673</v>
       </c>
+      <c r="E111"/>
       <c r="F111" t="s">
         <v>114</v>
       </c>
@@ -8278,6 +8304,7 @@
       <c r="D212">
         <v>1264047</v>
       </c>
+      <c r="E212"/>
       <c r="F212" t="s">
         <v>114</v>
       </c>
@@ -8301,6 +8328,7 @@
       <c r="D213">
         <v>1252930</v>
       </c>
+      <c r="E213"/>
       <c r="F213" t="s">
         <v>114</v>
       </c>
@@ -8324,6 +8352,7 @@
       <c r="D214">
         <v>1098822</v>
       </c>
+      <c r="E214"/>
       <c r="F214" t="s">
         <v>114</v>
       </c>
@@ -8347,6 +8376,7 @@
       <c r="D215">
         <v>1212743</v>
       </c>
+      <c r="E215"/>
       <c r="F215" t="s">
         <v>114</v>
       </c>
@@ -8370,6 +8400,7 @@
       <c r="D216">
         <v>1301543</v>
       </c>
+      <c r="E216"/>
       <c r="F216" t="s">
         <v>114</v>
       </c>
@@ -8393,6 +8424,7 @@
       <c r="D217">
         <v>1193423</v>
       </c>
+      <c r="E217"/>
       <c r="F217" t="s">
         <v>114</v>
       </c>
@@ -8416,6 +8448,7 @@
       <c r="D218">
         <v>1224976</v>
       </c>
+      <c r="E218"/>
       <c r="F218" t="s">
         <v>114</v>
       </c>
@@ -8439,6 +8472,7 @@
       <c r="D219">
         <v>1270121</v>
       </c>
+      <c r="E219"/>
       <c r="F219" t="s">
         <v>114</v>
       </c>
@@ -8462,6 +8496,7 @@
       <c r="D220">
         <v>1142510</v>
       </c>
+      <c r="E220"/>
       <c r="F220" t="s">
         <v>114</v>
       </c>
@@ -8485,6 +8520,7 @@
       <c r="D221">
         <v>1100637</v>
       </c>
+      <c r="E221"/>
       <c r="F221" t="s">
         <v>114</v>
       </c>
@@ -10068,6 +10104,7 @@
       <c r="D282">
         <v>1287793</v>
       </c>
+      <c r="E282"/>
       <c r="F282" t="s">
         <v>114</v>
       </c>
@@ -10091,6 +10128,7 @@
       <c r="D283">
         <v>1375722</v>
       </c>
+      <c r="E283"/>
       <c r="F283" t="s">
         <v>114</v>
       </c>
@@ -10114,6 +10152,7 @@
       <c r="D284">
         <v>1226861</v>
       </c>
+      <c r="E284"/>
       <c r="F284" t="s">
         <v>114</v>
       </c>
@@ -10137,6 +10176,7 @@
       <c r="D285">
         <v>1399992</v>
       </c>
+      <c r="E285"/>
       <c r="F285" t="s">
         <v>114</v>
       </c>
@@ -10160,6 +10200,7 @@
       <c r="D286">
         <v>1348479</v>
       </c>
+      <c r="E286"/>
       <c r="F286" t="s">
         <v>114</v>
       </c>
@@ -10183,6 +10224,7 @@
       <c r="D287">
         <v>1223670</v>
       </c>
+      <c r="E287"/>
       <c r="F287" t="s">
         <v>114</v>
       </c>
@@ -10206,6 +10248,7 @@
       <c r="D288">
         <v>1353478</v>
       </c>
+      <c r="E288"/>
       <c r="F288" t="s">
         <v>114</v>
       </c>
@@ -10229,6 +10272,7 @@
       <c r="D289">
         <v>1236756</v>
       </c>
+      <c r="E289"/>
       <c r="F289" t="s">
         <v>114</v>
       </c>
@@ -10252,6 +10296,7 @@
       <c r="D290">
         <v>1240693</v>
       </c>
+      <c r="E290"/>
       <c r="F290" t="s">
         <v>114</v>
       </c>
@@ -10275,6 +10320,7 @@
       <c r="D291">
         <v>1300522</v>
       </c>
+      <c r="E291"/>
       <c r="F291" t="s">
         <v>114</v>
       </c>
@@ -10289,26 +10335,26 @@
       <c r="A292" t="s">
         <v>304</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="3">
         <v>241</v>
       </c>
-      <c r="C292">
+      <c r="C292" s="3">
         <v>418116</v>
       </c>
-      <c r="D292">
+      <c r="D292" s="3">
         <v>1682502</v>
       </c>
-      <c r="E292">
+      <c r="E292" s="3">
         <v>54</v>
       </c>
-      <c r="F292" t="s">
-        <v>10</v>
-      </c>
-      <c r="G292">
+      <c r="F292" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G292" s="3">
         <v>14920.64</v>
       </c>
-      <c r="H292" t="s">
-        <v>44</v>
+      <c r="H292" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -10341,26 +10387,26 @@
       <c r="A294" t="s">
         <v>306</v>
       </c>
-      <c r="B294">
+      <c r="B294" s="3">
         <v>227</v>
       </c>
-      <c r="C294">
+      <c r="C294" s="3">
         <v>307985</v>
       </c>
-      <c r="D294">
+      <c r="D294" s="3">
         <v>1317175</v>
       </c>
-      <c r="E294">
-        <v>63</v>
-      </c>
-      <c r="F294" t="s">
-        <v>43</v>
-      </c>
-      <c r="G294">
-        <v>3601.23</v>
-      </c>
-      <c r="H294" t="s">
-        <v>44</v>
+      <c r="E294" s="3">
+        <v>58</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G294" s="3">
+        <v>12407.01</v>
+      </c>
+      <c r="H294" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -10523,25 +10569,25 @@
       <c r="A301" t="s">
         <v>313</v>
       </c>
-      <c r="B301">
+      <c r="B301" s="3">
         <v>250</v>
       </c>
-      <c r="C301">
+      <c r="C301" s="3">
         <v>432836</v>
       </c>
-      <c r="D301">
+      <c r="D301" s="3">
         <v>1755911</v>
       </c>
-      <c r="E301">
+      <c r="E301" s="3">
         <v>83</v>
       </c>
-      <c r="F301" t="s">
+      <c r="F301" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G301">
+      <c r="G301" s="3">
         <v>3601.22</v>
       </c>
-      <c r="H301" t="s">
+      <c r="H301" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -11078,6 +11124,7 @@
       <c r="D322">
         <v>1167412</v>
       </c>
+      <c r="E322"/>
       <c r="F322" t="s">
         <v>114</v>
       </c>
@@ -11101,6 +11148,7 @@
       <c r="D323">
         <v>1124465</v>
       </c>
+      <c r="E323"/>
       <c r="F323" t="s">
         <v>114</v>
       </c>
@@ -11124,6 +11172,7 @@
       <c r="D324">
         <v>1317470</v>
       </c>
+      <c r="E324"/>
       <c r="F324" t="s">
         <v>114</v>
       </c>
@@ -11147,6 +11196,7 @@
       <c r="D325">
         <v>1110181</v>
       </c>
+      <c r="E325"/>
       <c r="F325" t="s">
         <v>114</v>
       </c>
@@ -11170,6 +11220,7 @@
       <c r="D326">
         <v>1317130</v>
       </c>
+      <c r="E326"/>
       <c r="F326" t="s">
         <v>114</v>
       </c>
@@ -11193,6 +11244,7 @@
       <c r="D327">
         <v>1146198</v>
       </c>
+      <c r="E327"/>
       <c r="F327" t="s">
         <v>114</v>
       </c>
@@ -11216,6 +11268,7 @@
       <c r="D328">
         <v>1284400</v>
       </c>
+      <c r="E328"/>
       <c r="F328" t="s">
         <v>114</v>
       </c>
@@ -11239,6 +11292,7 @@
       <c r="D329">
         <v>1200526</v>
       </c>
+      <c r="E329"/>
       <c r="F329" t="s">
         <v>114</v>
       </c>
@@ -11262,6 +11316,7 @@
       <c r="D330">
         <v>1382486</v>
       </c>
+      <c r="E330"/>
       <c r="F330" t="s">
         <v>114</v>
       </c>
@@ -11285,6 +11340,7 @@
       <c r="D331">
         <v>1209061</v>
       </c>
+      <c r="E331"/>
       <c r="F331" t="s">
         <v>114</v>
       </c>
@@ -12625,26 +12681,26 @@
       <c r="A383" t="s">
         <v>395</v>
       </c>
-      <c r="B383">
+      <c r="B383" s="3">
         <v>240</v>
       </c>
-      <c r="C383">
+      <c r="C383" s="3">
         <v>426360</v>
       </c>
-      <c r="D383">
+      <c r="D383" s="3">
         <v>1722479</v>
       </c>
-      <c r="E383">
-        <v>49</v>
-      </c>
-      <c r="F383" t="s">
-        <v>43</v>
-      </c>
-      <c r="G383">
-        <v>3601.22</v>
-      </c>
-      <c r="H383" t="s">
-        <v>44</v>
+      <c r="E383" s="3">
+        <v>42</v>
+      </c>
+      <c r="F383" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G383" s="3">
+        <v>126214.66</v>
+      </c>
+      <c r="H383" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -12677,52 +12733,52 @@
       <c r="A385" t="s">
         <v>397</v>
       </c>
-      <c r="B385">
+      <c r="B385" s="3">
         <v>234</v>
       </c>
-      <c r="C385">
+      <c r="C385" s="3">
         <v>350181</v>
       </c>
-      <c r="D385">
+      <c r="D385" s="3">
         <v>1484536</v>
       </c>
-      <c r="E385">
-        <v>44</v>
-      </c>
-      <c r="F385" t="s">
-        <v>43</v>
-      </c>
-      <c r="G385">
-        <v>3601.22</v>
-      </c>
-      <c r="H385" t="s">
-        <v>44</v>
+      <c r="E385" s="3">
+        <v>42</v>
+      </c>
+      <c r="F385" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G385" s="3">
+        <v>2461.48</v>
+      </c>
+      <c r="H385" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>398</v>
       </c>
-      <c r="B386">
+      <c r="B386" s="3">
         <v>231</v>
       </c>
-      <c r="C386">
+      <c r="C386" s="3">
         <v>371134</v>
       </c>
-      <c r="D386">
+      <c r="D386" s="3">
         <v>1487369</v>
       </c>
-      <c r="E386">
-        <v>57</v>
-      </c>
-      <c r="F386" t="s">
-        <v>43</v>
-      </c>
-      <c r="G386">
-        <v>3601.22</v>
-      </c>
-      <c r="H386" t="s">
-        <v>44</v>
+      <c r="E386" s="3">
+        <v>49</v>
+      </c>
+      <c r="F386" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G386" s="3">
+        <v>8793.0499999999993</v>
+      </c>
+      <c r="H386" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -12755,26 +12811,26 @@
       <c r="A388" t="s">
         <v>400</v>
       </c>
-      <c r="B388">
+      <c r="B388" s="3">
         <v>246</v>
       </c>
-      <c r="C388">
+      <c r="C388" s="3">
         <v>406448</v>
       </c>
-      <c r="D388">
+      <c r="D388" s="3">
         <v>1666223</v>
       </c>
-      <c r="E388">
-        <v>54</v>
-      </c>
-      <c r="F388" t="s">
-        <v>43</v>
-      </c>
-      <c r="G388">
-        <v>3601.28</v>
-      </c>
-      <c r="H388" t="s">
-        <v>44</v>
+      <c r="E388" s="3">
+        <v>46</v>
+      </c>
+      <c r="F388" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G388" s="3">
+        <v>4702.34</v>
+      </c>
+      <c r="H388" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -12807,25 +12863,25 @@
       <c r="A390" t="s">
         <v>402</v>
       </c>
-      <c r="B390">
+      <c r="B390" s="3">
         <v>245</v>
       </c>
-      <c r="C390">
+      <c r="C390" s="3">
         <v>404028</v>
       </c>
-      <c r="D390">
+      <c r="D390" s="3">
         <v>1669323</v>
       </c>
-      <c r="E390">
+      <c r="E390" s="3">
         <v>51</v>
       </c>
-      <c r="F390" t="s">
+      <c r="F390" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G390">
+      <c r="G390" s="3">
         <v>3601.28</v>
       </c>
-      <c r="H390" t="s">
+      <c r="H390" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -13908,6 +13964,7 @@
       <c r="D432">
         <v>1146974</v>
       </c>
+      <c r="E432"/>
       <c r="F432" t="s">
         <v>114</v>
       </c>
@@ -13931,6 +13988,7 @@
       <c r="D433">
         <v>1248797</v>
       </c>
+      <c r="E433"/>
       <c r="F433" t="s">
         <v>114</v>
       </c>
@@ -13954,6 +14012,7 @@
       <c r="D434">
         <v>1379891</v>
       </c>
+      <c r="E434"/>
       <c r="F434" t="s">
         <v>114</v>
       </c>
@@ -13977,6 +14036,7 @@
       <c r="D435">
         <v>1290907</v>
       </c>
+      <c r="E435"/>
       <c r="F435" t="s">
         <v>114</v>
       </c>
@@ -14000,6 +14060,7 @@
       <c r="D436">
         <v>1296006</v>
       </c>
+      <c r="E436"/>
       <c r="F436" t="s">
         <v>114</v>
       </c>
@@ -14023,6 +14084,7 @@
       <c r="D437">
         <v>1313411</v>
       </c>
+      <c r="E437"/>
       <c r="F437" t="s">
         <v>114</v>
       </c>
@@ -14046,6 +14108,7 @@
       <c r="D438">
         <v>1428414</v>
       </c>
+      <c r="E438"/>
       <c r="F438" t="s">
         <v>114</v>
       </c>
@@ -14069,6 +14132,7 @@
       <c r="D439">
         <v>1325995</v>
       </c>
+      <c r="E439"/>
       <c r="F439" t="s">
         <v>114</v>
       </c>
@@ -14092,6 +14156,7 @@
       <c r="D440">
         <v>1350966</v>
       </c>
+      <c r="E440"/>
       <c r="F440" t="s">
         <v>114</v>
       </c>
@@ -14115,6 +14180,7 @@
       <c r="D441">
         <v>1210319</v>
       </c>
+      <c r="E441"/>
       <c r="F441" t="s">
         <v>114</v>
       </c>
@@ -16738,6 +16804,7 @@
       <c r="D542">
         <v>1669338</v>
       </c>
+      <c r="E542"/>
       <c r="F542" t="s">
         <v>114</v>
       </c>
@@ -16761,6 +16828,7 @@
       <c r="D543">
         <v>1638801</v>
       </c>
+      <c r="E543"/>
       <c r="F543" t="s">
         <v>114</v>
       </c>
@@ -16784,6 +16852,7 @@
       <c r="D544">
         <v>1714588</v>
       </c>
+      <c r="E544"/>
       <c r="F544" t="s">
         <v>114</v>
       </c>
@@ -16807,6 +16876,7 @@
       <c r="D545">
         <v>1740442</v>
       </c>
+      <c r="E545"/>
       <c r="F545" t="s">
         <v>114</v>
       </c>
@@ -16830,6 +16900,7 @@
       <c r="D546">
         <v>1702235</v>
       </c>
+      <c r="E546"/>
       <c r="F546" t="s">
         <v>114</v>
       </c>
@@ -16853,6 +16924,7 @@
       <c r="D547">
         <v>1835879</v>
       </c>
+      <c r="E547"/>
       <c r="F547" t="s">
         <v>114</v>
       </c>
@@ -16876,6 +16948,7 @@
       <c r="D548">
         <v>1566965</v>
       </c>
+      <c r="E548"/>
       <c r="F548" t="s">
         <v>114</v>
       </c>
@@ -16899,6 +16972,7 @@
       <c r="D549">
         <v>1850913</v>
       </c>
+      <c r="E549"/>
       <c r="F549" t="s">
         <v>114</v>
       </c>
@@ -16922,6 +16996,7 @@
       <c r="D550">
         <v>1695479</v>
       </c>
+      <c r="E550"/>
       <c r="F550" t="s">
         <v>114</v>
       </c>
@@ -16945,6 +17020,7 @@
       <c r="D551">
         <v>1787727</v>
       </c>
+      <c r="E551"/>
       <c r="F551" t="s">
         <v>114</v>
       </c>
@@ -18268,6 +18344,7 @@
       <c r="D602">
         <v>1687943</v>
       </c>
+      <c r="E602"/>
       <c r="F602" t="s">
         <v>114</v>
       </c>
@@ -18291,6 +18368,7 @@
       <c r="D603">
         <v>1790633</v>
       </c>
+      <c r="E603"/>
       <c r="F603" t="s">
         <v>114</v>
       </c>
@@ -18314,6 +18392,7 @@
       <c r="D604">
         <v>1652847</v>
       </c>
+      <c r="E604"/>
       <c r="F604" t="s">
         <v>114</v>
       </c>
@@ -18337,6 +18416,7 @@
       <c r="D605">
         <v>1856442</v>
       </c>
+      <c r="E605"/>
       <c r="F605" t="s">
         <v>114</v>
       </c>
@@ -18360,6 +18440,7 @@
       <c r="D606">
         <v>1529071</v>
       </c>
+      <c r="E606"/>
       <c r="F606" t="s">
         <v>114</v>
       </c>
@@ -18383,6 +18464,7 @@
       <c r="D607">
         <v>1769478</v>
       </c>
+      <c r="E607"/>
       <c r="F607" t="s">
         <v>114</v>
       </c>
@@ -18406,6 +18488,7 @@
       <c r="D608">
         <v>1631661</v>
       </c>
+      <c r="E608"/>
       <c r="F608" t="s">
         <v>114</v>
       </c>
@@ -18429,6 +18512,7 @@
       <c r="D609">
         <v>1850336</v>
       </c>
+      <c r="E609"/>
       <c r="F609" t="s">
         <v>114</v>
       </c>
@@ -18452,6 +18536,7 @@
       <c r="D610">
         <v>1990290</v>
       </c>
+      <c r="E610"/>
       <c r="F610" t="s">
         <v>114</v>
       </c>
@@ -18475,6 +18560,7 @@
       <c r="D611">
         <v>1737060</v>
       </c>
+      <c r="E611"/>
       <c r="F611" t="s">
         <v>114</v>
       </c>
@@ -18498,6 +18584,7 @@
       <c r="D612">
         <v>1785752</v>
       </c>
+      <c r="E612"/>
       <c r="F612" t="s">
         <v>114</v>
       </c>
@@ -18521,6 +18608,7 @@
       <c r="D613">
         <v>1925553</v>
       </c>
+      <c r="E613"/>
       <c r="F613" t="s">
         <v>114</v>
       </c>
@@ -18544,6 +18632,7 @@
       <c r="D614">
         <v>1646495</v>
       </c>
+      <c r="E614"/>
       <c r="F614" t="s">
         <v>114</v>
       </c>
@@ -18567,6 +18656,7 @@
       <c r="D615">
         <v>1926815</v>
       </c>
+      <c r="E615"/>
       <c r="F615" t="s">
         <v>114</v>
       </c>
@@ -18590,6 +18680,7 @@
       <c r="D616">
         <v>1963096</v>
       </c>
+      <c r="E616"/>
       <c r="F616" t="s">
         <v>114</v>
       </c>
@@ -18613,6 +18704,7 @@
       <c r="D617">
         <v>1994476</v>
       </c>
+      <c r="E617"/>
       <c r="F617" t="s">
         <v>114</v>
       </c>
@@ -18636,6 +18728,7 @@
       <c r="D618">
         <v>1626340</v>
       </c>
+      <c r="E618"/>
       <c r="F618" t="s">
         <v>114</v>
       </c>
@@ -18659,6 +18752,7 @@
       <c r="D619">
         <v>1957971</v>
       </c>
+      <c r="E619"/>
       <c r="F619" t="s">
         <v>114</v>
       </c>
@@ -18708,6 +18802,7 @@
       <c r="D621">
         <v>1742207</v>
       </c>
+      <c r="E621"/>
       <c r="F621" t="s">
         <v>114</v>
       </c>
@@ -18731,6 +18826,7 @@
       <c r="D622">
         <v>2045258</v>
       </c>
+      <c r="E622"/>
       <c r="F622" t="s">
         <v>114</v>
       </c>
@@ -18754,6 +18850,7 @@
       <c r="D623">
         <v>1835527</v>
       </c>
+      <c r="E623"/>
       <c r="F623" t="s">
         <v>114</v>
       </c>
@@ -18777,6 +18874,7 @@
       <c r="D624">
         <v>2015633</v>
       </c>
+      <c r="E624"/>
       <c r="F624" t="s">
         <v>114</v>
       </c>
@@ -18800,6 +18898,7 @@
       <c r="D625">
         <v>1988944</v>
       </c>
+      <c r="E625"/>
       <c r="F625" t="s">
         <v>114</v>
       </c>
@@ -18823,6 +18922,7 @@
       <c r="D626">
         <v>1742700</v>
       </c>
+      <c r="E626"/>
       <c r="F626" t="s">
         <v>114</v>
       </c>
@@ -18846,6 +18946,7 @@
       <c r="D627">
         <v>2116056</v>
       </c>
+      <c r="E627"/>
       <c r="F627" t="s">
         <v>114</v>
       </c>
@@ -18895,6 +18996,7 @@
       <c r="D629">
         <v>1914414</v>
       </c>
+      <c r="E629"/>
       <c r="F629" t="s">
         <v>114</v>
       </c>
@@ -18918,6 +19020,7 @@
       <c r="D630">
         <v>1937487</v>
       </c>
+      <c r="E630"/>
       <c r="F630" t="s">
         <v>114</v>
       </c>
@@ -18941,6 +19044,7 @@
       <c r="D631">
         <v>1770384</v>
       </c>
+      <c r="E631"/>
       <c r="F631" t="s">
         <v>114</v>
       </c>
